--- a/정보Table.xlsx
+++ b/정보Table.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D475"/>
+  <dimension ref="A1:D476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="32.75" customWidth="1" min="1" max="1"/>
@@ -9657,7 +9657,28 @@
       <c r="C475" s="2" t="n"/>
       <c r="D475" s="2" t="n"/>
     </row>
-    <row r="476" ht="27" customHeight="1"/>
+    <row r="476" ht="27" customHeight="1">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>고대의 빙마 그린워스</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>혹한 - 빙하기의 왕관</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>아이템</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>신화</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
